--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:18:10+00:00</t>
+    <t>2023-04-28T11:24:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:11+00:00</t>
+    <t>2023-04-28T11:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:31+00:00</t>
+    <t>2023-04-30T03:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:40+00:00</t>
+    <t>2023-04-30T03:44:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:58+00:00</t>
+    <t>2023-04-30T03:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:52:18+00:00</t>
+    <t>2023-04-30T03:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:53:51+00:00</t>
+    <t>2023-04-30T09:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T09:28:44+00:00</t>
+    <t>2023-05-01T08:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:52:03+00:00</t>
+    <t>2023-05-01T08:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:56:42+00:00</t>
+    <t>2023-05-01T09:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:10:15+00:00</t>
+    <t>2023-05-01T09:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:11:26+00:00</t>
+    <t>2023-05-01T09:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:13:53+00:00</t>
+    <t>2023-05-01T09:16:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:16:45+00:00</t>
+    <t>2023-05-01T16:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:06+00:00</t>
+    <t>2023-05-01T16:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:27+00:00</t>
+    <t>2023-05-01T18:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:00+00:00</t>
+    <t>2023-05-01T18:12:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:07+00:00</t>
+    <t>2023-05-02T21:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:42:53+00:00</t>
+    <t>2023-05-05T21:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$38</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="361">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,33 +431,57 @@
     <t>DiagnosticReport.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:TestedByIndex</t>
+  </si>
+  <si>
+    <t>TestedByIndex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/tested-by-user-index}
+</t>
+  </si>
+  <si>
+    <t>HIV Viral Load Result Tested By</t>
+  </si>
+  <si>
+    <t>The user index for the person who tested the viral load specimen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -465,6 +489,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -550,9 +577,6 @@
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
   </si>
   <si>
-    <t>final</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
@@ -659,17 +683,13 @@
     <t>DiagnosticReport.code.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1444,12 +1464,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AN38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.37890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.69140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.37890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1457,7 +1477,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="60.13671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.89453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2415,11 +2435,11 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2434,17 +2454,15 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>80</v>
@@ -2481,16 +2499,14 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>139</v>
@@ -2514,7 +2530,7 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>80</v>
@@ -2525,43 +2541,41 @@
         <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>80</v>
       </c>
@@ -2609,7 +2623,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2618,7 +2632,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>140</v>
@@ -2630,7 +2644,7 @@
         <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>80</v>
@@ -2638,14 +2652,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2658,13 +2672,13 @@
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>149</v>
@@ -2725,7 +2739,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2737,31 +2751,31 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2777,22 +2791,22 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -2841,7 +2855,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2856,47 +2870,47 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>168</v>
@@ -2904,9 +2918,11 @@
       <c r="M13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -2916,7 +2932,7 @@
         <v>80</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>80</v>
@@ -2931,13 +2947,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -2955,13 +2971,13 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>80</v>
@@ -2970,58 +2986,58 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="AN13" t="s" s="2">
-        <v>177</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3045,13 +3061,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3069,13 +3085,13 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
@@ -3084,35 +3100,35 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>80</v>
@@ -3124,15 +3140,17 @@
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3157,11 +3175,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3179,13 +3199,13 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
@@ -3194,32 +3214,32 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>198</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>89</v>
@@ -3231,16 +3251,16 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3267,13 +3287,11 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3291,10 +3309,10 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>89</v>
@@ -3303,38 +3321,38 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>204</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -3346,17 +3364,15 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3393,16 +3409,16 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>210</v>
@@ -3411,13 +3427,13 @@
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
@@ -3426,7 +3442,7 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -3434,14 +3450,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3457,10 +3473,10 @@
         <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>213</v>
@@ -3469,11 +3485,9 @@
         <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
       </c>
@@ -3509,19 +3523,19 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3533,16 +3547,16 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>80</v>
@@ -3550,10 +3564,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3564,7 +3578,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>80</v>
@@ -3576,19 +3590,19 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3598,7 +3612,7 @@
         <v>80</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>80</v>
@@ -3637,13 +3651,13 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>80</v>
@@ -3655,10 +3669,10 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
@@ -3666,18 +3680,18 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -3692,17 +3706,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3712,7 +3728,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -3751,7 +3767,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3766,28 +3782,28 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>238</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3806,19 +3822,17 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -3867,7 +3881,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3882,32 +3896,32 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>89</v>
@@ -3922,19 +3936,19 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -3983,7 +3997,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3998,28 +4012,28 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4038,19 +4052,19 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4099,7 +4113,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4114,35 +4128,35 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G24" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4154,19 +4168,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4215,13 +4229,13 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
@@ -4230,32 +4244,32 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>278</v>
+        <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -4270,19 +4284,19 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4331,7 +4345,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4346,16 +4360,16 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4367,7 +4381,7 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4383,10 +4397,10 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>290</v>
@@ -4398,7 +4412,7 @@
         <v>292</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4462,35 +4476,35 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>237</v>
+        <v>286</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>80</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>296</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -4502,19 +4516,19 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4563,7 +4577,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4581,10 +4595,10 @@
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4592,21 +4606,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -4618,18 +4632,20 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="N28" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
       </c>
@@ -4677,7 +4693,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4695,7 +4711,7 @@
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>80</v>
+        <v>308</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>309</v>
@@ -4713,7 +4729,7 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>311</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4729,21 +4745,21 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -4809,10 +4825,10 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -4820,21 +4836,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -4843,19 +4859,21 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>200</v>
+        <v>318</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>201</v>
+        <v>319</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>202</v>
+        <v>320</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4903,28 +4921,28 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -4932,21 +4950,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -4958,17 +4976,15 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5023,13 +5039,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5038,7 +5054,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5046,14 +5062,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>320</v>
+        <v>148</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5066,26 +5082,24 @@
         <v>80</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>213</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>214</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5133,7 +5147,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>323</v>
+        <v>216</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5154,7 +5168,7 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>132</v>
+        <v>211</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5162,45 +5176,45 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>200</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>327</v>
+        <v>151</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>328</v>
+        <v>152</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5249,19 +5263,19 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -5270,7 +5284,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>329</v>
+        <v>132</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5289,7 +5303,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
@@ -5301,19 +5315,23 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
@@ -5364,7 +5382,7 @@
         <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>89</v>
@@ -5382,7 +5400,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5390,44 +5408,42 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>336</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>200</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>339</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -5475,10 +5491,10 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>89</v>
@@ -5493,10 +5509,10 @@
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5504,24 +5520,24 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
@@ -5530,7 +5546,7 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>343</v>
@@ -5539,7 +5555,9 @@
         <v>344</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5563,13 +5581,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>345</v>
+        <v>80</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5587,13 +5605,13 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
@@ -5605,7 +5623,7 @@
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>347</v>
@@ -5642,20 +5660,16 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>353</v>
-      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5679,13 +5693,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -5721,17 +5735,133 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="B38" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN37">
+  <autoFilter ref="A1:AN38">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5741,7 +5871,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI36">
+  <conditionalFormatting sqref="A2:AI37">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="365">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -284,6 +284,9 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>DiagnosticReport.id</t>
   </si>
   <si>
@@ -367,7 +370,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -425,6 +428,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -475,6 +482,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>DiagnosticReport.modifierExtension</t>
   </si>
   <si>
@@ -492,7 +503,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -580,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status|4.3.0</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -618,7 +629,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>Codes for diagnostic service sections.</t>
+    <t>HL7 V2 table 0074</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
@@ -664,68 +675,68 @@
     <t>DiagnosticReport.code.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.text</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code.text</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -757,7 +768,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
 </t>
   </si>
   <si>
@@ -974,7 +985,7 @@
     <t>Observations</t>
   </si>
   <si>
-    <t>[Observations](http://hl7.org/fhir/R4/observation.html)  that are part of this diagnostic report.</t>
+    <t>[Observations](http://hl7.org/fhir/R4B/observation.html)  that are part of this diagnostic report.</t>
   </si>
   <si>
     <t>Observations can contain observations.</t>
@@ -1028,6 +1039,10 @@
     <t>Many diagnostic services include images in the report as part of their service.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
+  </si>
+  <si>
     <t>OBX?</t>
   </si>
   <si>
@@ -1119,7 +1134,7 @@
     <t>One or more codes that represent the summary conclusion (interpretation/impression) of the diagnostic report.</t>
   </si>
   <si>
-    <t>Diagnosis codes provided as adjuncts to the report.</t>
+    <t>SNOMED CT Clinical Findings</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
@@ -1477,7 +1492,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.89453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="94.21484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1491,7 +1506,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="48.453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="33.43359375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="53.5625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1741,15 +1756,15 @@
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1760,7 +1775,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>80</v>
@@ -1769,19 +1784,19 @@
         <v>80</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1831,13 +1846,13 @@
         <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>80</v>
@@ -1860,10 +1875,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1874,7 +1889,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>80</v>
@@ -1883,16 +1898,16 @@
         <v>80</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1943,19 +1958,19 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -1972,10 +1987,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1986,28 +2001,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2057,19 +2072,19 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2086,10 +2101,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2100,7 +2115,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2112,16 +2127,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2147,13 +2162,13 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>80</v>
@@ -2171,19 +2186,19 @@
         <v>80</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -2200,21 +2215,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>80</v>
@@ -2226,16 +2241,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2285,19 +2300,19 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>80</v>
@@ -2306,7 +2321,7 @@
         <v>80</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>80</v>
@@ -2314,14 +2329,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2340,16 +2355,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2399,7 +2414,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2411,7 +2426,7 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
@@ -2420,7 +2435,7 @@
         <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>80</v>
@@ -2428,10 +2443,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2439,7 +2454,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2454,13 +2469,13 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2499,17 +2514,17 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2521,7 +2536,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -2538,23 +2553,23 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>80</v>
@@ -2566,13 +2581,13 @@
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2623,7 +2638,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2632,10 +2647,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -2652,14 +2667,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2672,25 +2687,25 @@
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -2739,7 +2754,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2751,7 +2766,7 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -2760,7 +2775,7 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>80</v>
@@ -2768,14 +2783,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2791,22 +2806,22 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -2855,7 +2870,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2867,31 +2882,31 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2910,19 +2925,19 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -2971,7 +2986,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2983,16 +2998,16 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
@@ -3000,10 +3015,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3011,32 +3026,32 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3061,13 +3076,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3085,43 +3100,43 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3137,19 +3152,19 @@
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3175,13 +3190,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3199,7 +3214,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3211,38 +3226,38 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -3251,16 +3266,16 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3287,11 +3302,11 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3309,39 +3324,39 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3352,7 +3367,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -3364,13 +3379,13 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>207</v>
+        <v>92</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3421,13 +3436,13 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
@@ -3442,7 +3457,7 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -3450,14 +3465,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3476,16 +3491,16 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3523,19 +3538,19 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3547,7 +3562,7 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
@@ -3556,7 +3571,7 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>80</v>
@@ -3564,10 +3579,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3587,22 +3602,22 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3651,7 +3666,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3663,16 +3678,16 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
@@ -3680,10 +3695,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3694,7 +3709,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -3703,22 +3718,22 @@
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3728,7 +3743,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -3767,28 +3782,28 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
@@ -3796,21 +3811,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>80</v>
@@ -3819,20 +3834,20 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -3881,50 +3896,50 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -3933,22 +3948,22 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -3997,50 +4012,50 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>80</v>
@@ -4049,22 +4064,22 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4113,50 +4128,50 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4165,22 +4180,22 @@
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4229,47 +4244,47 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -4281,22 +4296,22 @@
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4345,7 +4360,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4357,35 +4372,35 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -4397,22 +4412,22 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4461,7 +4476,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4473,27 +4488,27 @@
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4516,19 +4531,19 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4577,7 +4592,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4589,16 +4604,16 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4606,21 +4621,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -4632,19 +4647,19 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -4693,7 +4708,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4705,16 +4720,16 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
@@ -4722,10 +4737,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4748,16 +4763,16 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4807,7 +4822,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4819,7 +4834,7 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -4828,7 +4843,7 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -4836,14 +4851,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4859,20 +4874,20 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -4921,7 +4936,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4933,16 +4948,16 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>325</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -4950,10 +4965,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4964,7 +4979,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -4976,13 +4991,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5033,13 +5048,13 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
@@ -5054,7 +5069,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5062,14 +5077,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5088,16 +5103,16 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5147,7 +5162,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5159,7 +5174,7 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
@@ -5168,7 +5183,7 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5176,14 +5191,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5196,25 +5211,25 @@
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5263,7 +5278,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5275,7 +5290,7 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -5284,7 +5299,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5292,10 +5307,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5306,7 +5321,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5318,19 +5333,19 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5379,19 +5394,19 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -5400,7 +5415,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5408,10 +5423,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5419,10 +5434,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
@@ -5431,16 +5446,16 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5491,19 +5506,19 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
@@ -5512,7 +5527,7 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5520,24 +5535,24 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
@@ -5546,17 +5561,17 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -5605,28 +5620,28 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -5634,10 +5649,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5660,13 +5675,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5693,31 +5708,31 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Z37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5729,16 +5744,16 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -5746,10 +5761,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5772,19 +5787,19 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -5833,7 +5848,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5845,16 +5860,16 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="361">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -284,9 +284,6 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>clinical.diagnostics</t>
-  </si>
-  <si>
     <t>DiagnosticReport.id</t>
   </si>
   <si>
@@ -370,7 +367,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -428,10 +425,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -482,10 +475,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>DiagnosticReport.modifierExtension</t>
   </si>
   <si>
@@ -503,7 +492,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -591,7 +580,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -629,7 +618,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>HL7 V2 table 0074</t>
+    <t>Codes for diagnostic service sections.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
@@ -675,6 +664,10 @@
     <t>DiagnosticReport.code.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -733,10 +726,6 @@
     <t>DiagnosticReport.code.text</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -768,7 +757,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
 </t>
   </si>
   <si>
@@ -985,7 +974,7 @@
     <t>Observations</t>
   </si>
   <si>
-    <t>[Observations](http://hl7.org/fhir/R4B/observation.html)  that are part of this diagnostic report.</t>
+    <t>[Observations](http://hl7.org/fhir/R4/observation.html)  that are part of this diagnostic report.</t>
   </si>
   <si>
     <t>Observations can contain observations.</t>
@@ -1039,10 +1028,6 @@
     <t>Many diagnostic services include images in the report as part of their service.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
-  </si>
-  <si>
     <t>OBX?</t>
   </si>
   <si>
@@ -1134,7 +1119,7 @@
     <t>One or more codes that represent the summary conclusion (interpretation/impression) of the diagnostic report.</t>
   </si>
   <si>
-    <t>SNOMED CT Clinical Findings</t>
+    <t>Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
@@ -1492,7 +1477,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.21484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.89453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1506,7 +1491,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="33.43359375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="48.453125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="53.5625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1756,15 +1741,15 @@
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1775,28 +1760,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1846,13 +1831,13 @@
         <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>80</v>
@@ -1875,10 +1860,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1889,25 +1874,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1958,19 +1943,19 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -1987,10 +1972,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2001,28 +1986,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2072,19 +2057,19 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2101,10 +2086,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2115,7 +2100,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2127,16 +2112,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2162,43 +2147,43 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>117</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -2215,21 +2200,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>80</v>
@@ -2241,16 +2226,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2300,28 +2285,28 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>80</v>
@@ -2329,14 +2314,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2355,16 +2340,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2414,7 +2399,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2426,7 +2411,7 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
@@ -2435,7 +2420,7 @@
         <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>80</v>
@@ -2443,10 +2428,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2454,7 +2439,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2469,13 +2454,13 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2514,17 +2499,17 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2536,7 +2521,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -2553,23 +2538,23 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>80</v>
@@ -2581,13 +2566,13 @@
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2638,7 +2623,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2647,10 +2632,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -2667,14 +2652,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2687,25 +2672,25 @@
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -2754,7 +2739,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2766,7 +2751,7 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -2775,7 +2760,7 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>80</v>
@@ -2783,14 +2768,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2806,22 +2791,22 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -2870,7 +2855,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2882,31 +2867,31 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>167</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2925,19 +2910,19 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -2986,7 +2971,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2998,16 +2983,16 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
@@ -3015,10 +3000,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3026,32 +3011,32 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="J14" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3076,67 +3061,67 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Y14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>187</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3152,19 +3137,19 @@
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3190,13 +3175,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3214,7 +3199,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3226,56 +3211,56 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3302,61 +3287,61 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>208</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3367,7 +3352,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -3379,13 +3364,13 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3436,13 +3421,13 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
@@ -3457,7 +3442,7 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -3465,14 +3450,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3491,16 +3476,16 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3538,19 +3523,19 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3562,7 +3547,7 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
@@ -3571,7 +3556,7 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>80</v>
@@ -3579,10 +3564,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3602,22 +3587,22 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3666,7 +3651,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3678,16 +3663,16 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
@@ -3695,10 +3680,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3709,31 +3694,31 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3743,67 +3728,67 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
@@ -3811,43 +3796,43 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G21" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -3896,74 +3881,74 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G22" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K22" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4012,74 +3997,74 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4128,74 +4113,74 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>269</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4244,47 +4229,47 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -4296,22 +4281,22 @@
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4360,7 +4345,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4372,35 +4357,35 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -4412,22 +4397,22 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4476,7 +4461,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4488,27 +4473,27 @@
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4531,19 +4516,19 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4592,7 +4577,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4604,16 +4589,16 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4621,21 +4606,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -4647,19 +4632,19 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -4708,7 +4693,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4720,16 +4705,16 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
@@ -4737,10 +4722,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4763,16 +4748,16 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4822,7 +4807,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4834,7 +4819,7 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -4843,7 +4828,7 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -4851,14 +4836,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4874,20 +4859,20 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -4936,7 +4921,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4948,16 +4933,16 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>325</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -4965,10 +4950,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4979,7 +4964,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -4991,13 +4976,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5048,13 +5033,13 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
@@ -5069,7 +5054,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5077,14 +5062,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5103,16 +5088,16 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5162,7 +5147,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5174,7 +5159,7 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
@@ -5183,7 +5168,7 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5191,14 +5176,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5211,25 +5196,25 @@
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5278,7 +5263,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5290,7 +5275,7 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -5299,7 +5284,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5307,10 +5292,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5321,7 +5306,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5333,19 +5318,19 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5394,19 +5379,19 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -5415,7 +5400,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5423,10 +5408,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5434,28 +5419,28 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G35" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5506,28 +5491,28 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5535,25 +5520,25 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H36" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5561,17 +5546,17 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -5620,28 +5605,28 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -5649,10 +5634,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5675,13 +5660,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5708,13 +5693,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -5732,7 +5717,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5744,16 +5729,16 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -5761,10 +5746,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5787,19 +5772,19 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O38" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -5848,7 +5833,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5860,16 +5845,16 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>

--- a/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
